--- a/Employee_Reports_wi48/Niroshan Abesingha Abesingha Karunarathna Mudalige Q0571.xlsx
+++ b/Employee_Reports_wi48/Niroshan Abesingha Abesingha Karunarathna Mudalige Q0571.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-59</v>
+        <v>-62</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -789,53 +789,53 @@
       <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-M-013</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>28-May-2024</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>28-May-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>-46</v>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>08-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>632</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-89</v>
+        <v>-92</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-44</v>
+        <v>-47</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-45</v>
+        <v>-48</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1546,11 +1546,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1595,11 +1595,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1644,11 +1644,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-95</v>
+        <v>-98</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1791,11 +1791,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1889,11 +1889,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1926,11 +1926,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1975,11 +1975,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2024,11 +2024,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2061,11 +2061,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2172,11 +2172,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
